--- a/data/trans_camb/IP16B04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B04-Clase-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Grupo IV y V</t>
+          <t>Grupo VI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1061,27 +1061,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Grupo VII</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>No ha trabajado</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1373,32 +1373,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1449,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1517,177 +1517,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>
